--- a/docs/Anvil/pythonfiles/insultkit.xlsx
+++ b/docs/Anvil/pythonfiles/insultkit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://paradevic-my.sharepoint.com/personal/gmccarthy_parade_vic_edu_au/Documents/All DT/microbit for online/PC-app-development/docs/Anvil/pythonfiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{59D4F145-340B-46D1-AEE9-0D8AB2A0101C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86F0D0DD-F89D-47AE-9F64-5A95B3A66C1A}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{59D4F145-340B-46D1-AEE9-0D8AB2A0101C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D8809C3-BA53-41F5-99C9-C8352F287288}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="720" windowWidth="10815" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet5" sheetId="7" r:id="rId1"/>
@@ -463,13 +463,13 @@
     <t>slippery eel</t>
   </si>
   <si>
-    <t>Insult1</t>
-  </si>
-  <si>
-    <t>Insult2</t>
-  </si>
-  <si>
-    <t>Insult3</t>
+    <t>term1</t>
+  </si>
+  <si>
+    <t>term2</t>
+  </si>
+  <si>
+    <t>term3</t>
   </si>
 </sst>
 </file>
